--- a/data/trans_camb/P14B23-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Provincia-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,21</t>
+          <t>-3,23; 2,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,59</t>
+          <t>-4,13; 0,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,12</t>
+          <t>-3,51; 7,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,25</t>
+          <t>-8,97; -1,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,85</t>
+          <t>-2,5; 3,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,92</t>
+          <t>-5,75; -1,21</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,91; 152,63</t>
+          <t>-73,07; 137,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,78; 53,2</t>
+          <t>-89,26; 51,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 91,99</t>
+          <t>-31,31; 111,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,09; -17,95</t>
+          <t>-70,97; -15,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 78,39</t>
+          <t>-34,5; 78,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,61; -19,07</t>
+          <t>-70,26; -20,12</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,68</t>
+          <t>-3,54; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,17</t>
+          <t>-2,28; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,52</t>
+          <t>-5,81; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,46</t>
+          <t>-3,14; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,06</t>
+          <t>-3,6; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,89</t>
+          <t>-2,13; 2,52</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 100,72</t>
+          <t>-69,55; 80,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 171,3</t>
+          <t>-48,26; 156,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 18,52</t>
+          <t>-45,8; 19,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 40,33</t>
+          <t>-24,38; 46,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 18,18</t>
+          <t>-44,69; 16,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 53,41</t>
+          <t>-25,3; 44,04</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,24</t>
+          <t>-4,7; -0,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 6,32</t>
+          <t>-0,37; 5,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,75</t>
+          <t>-4,67; 2,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,16</t>
+          <t>-3,82; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,84</t>
+          <t>-3,7; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,84</t>
+          <t>-1,02; 3,81</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,05; 10,85</t>
+          <t>-94,32; 30,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 321,28</t>
+          <t>-14,45; 315,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 64,32</t>
+          <t>-57,55; 67,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 72,34</t>
+          <t>-42,39; 64,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 28,23</t>
+          <t>-64,56; 19,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 113,09</t>
+          <t>-20,16; 105,5</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,23</t>
+          <t>-0,42; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,42</t>
+          <t>2,1; 7,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -0,35</t>
+          <t>-7,77; -0,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,31</t>
+          <t>-6,06; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,35</t>
+          <t>-3,54; 0,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,16</t>
+          <t>-0,9; 4,13</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>99,24; —</t>
+          <t>103,14; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,94; -1,39</t>
+          <t>-70,71; -8,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 34,65</t>
+          <t>-55,15; 35,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 15,04</t>
+          <t>-60,55; 15,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 112,5</t>
+          <t>-14,57; 111,11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,82</t>
+          <t>-2,01; 5,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,23</t>
+          <t>-5,8; 0,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,91; -1,96</t>
+          <t>-14,37; -1,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,3; -7,39</t>
+          <t>-18,32; -7,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,11</t>
+          <t>-6,72; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -4,3</t>
+          <t>-10,38; -4,32</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 388,25</t>
+          <t>-42,51; 317,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,8; 55,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,34; -13,05</t>
+          <t>-72,37; -12,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-89,74; -62,18</t>
+          <t>-89,38; -60,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,65; 3,36</t>
+          <t>-56,96; 5,87</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,01; -56,09</t>
+          <t>-84,94; -54,99</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; -0,23</t>
+          <t>-4,97; -0,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,34</t>
+          <t>-0,83; 5,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 6,38</t>
+          <t>-3,31; 6,56</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,36</t>
+          <t>-5,82; 2,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,35</t>
+          <t>-3,23; 2,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,99</t>
+          <t>-2,28; 3,07</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,47</t>
+          <t>-100,0; 15,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 277,57</t>
+          <t>-26,03; 291,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 105,94</t>
+          <t>-32,1; 115,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 46,21</t>
+          <t>-52,12; 40,09</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 53,64</t>
+          <t>-43,97; 43,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 67,43</t>
+          <t>-30,22; 74,13</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,04</t>
+          <t>-2,97; -0,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,75</t>
+          <t>0,18; 4,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,9</t>
+          <t>-4,23; 0,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,47</t>
+          <t>-2,54; 5,65</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,08</t>
+          <t>-3,06; -0,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,35</t>
+          <t>-0,46; 4,53</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-85,08; 20,95</t>
+          <t>-86,82; 12,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 258,25</t>
+          <t>-1,78; 281,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 19,9</t>
+          <t>-58,55; 19,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 105,2</t>
+          <t>-40,52; 112,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,36; -1,41</t>
+          <t>-61,4; -1,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 118,04</t>
+          <t>-6,26; 127,81</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,65</t>
+          <t>-1,23; 1,8</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,39</t>
+          <t>-1,84; 1,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,81</t>
+          <t>-2,17; 2,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,39</t>
+          <t>-1,6; 3,03</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,77</t>
+          <t>-1,15; 1,73</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,58</t>
+          <t>-1,91; 1,65</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 147,11</t>
+          <t>-48,21; 162,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,39; 102,98</t>
+          <t>-65,55; 123,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 58,93</t>
+          <t>-28,77; 50,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 69,06</t>
+          <t>-22,0; 61,41</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 53,44</t>
+          <t>-24,37; 51,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 44,55</t>
+          <t>-38,38; 46,75</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,25</t>
+          <t>-1,23; 0,29</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,1</t>
+          <t>0,14; 2,1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,05</t>
+          <t>-2,66; -0,08</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,45</t>
+          <t>-2,43; 0,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,15</t>
+          <t>-1,74; -0,25</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,0</t>
+          <t>-0,68; 1,07</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 13,37</t>
+          <t>-43,33; 13,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3,49; 99,1</t>
+          <t>4,66; 95,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,62; -0,58</t>
+          <t>-30,63; -1,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 6,4</t>
+          <t>-28,27; 5,49</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -3,12</t>
+          <t>-30,04; -4,63</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 20,39</t>
+          <t>-11,83; 21,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P14B23-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P14B23-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-4,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,18</t>
+          <t>-3,25</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,41</t>
+          <t>-3,2; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,71</t>
+          <t>-4,28; 0,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,31</t>
+          <t>-3,84; 6,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -1,18</t>
+          <t>-8,77; -1,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,68</t>
+          <t>-2,64; 3,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,75; -1,21</t>
+          <t>-5,49; -1,19</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-51,59%</t>
+          <t>-56,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-51,39%</t>
+          <t>-52,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-51,97%</t>
+          <t>-53,05%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 137,89</t>
+          <t>-72,98; 164,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-89,26; 51,49</t>
+          <t>-88,45; 34,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 111,02</t>
+          <t>-34,81; 88,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,97; -15,24</t>
+          <t>-72,65; -18,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 78,54</t>
+          <t>-33,82; 81,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,26; -20,12</t>
+          <t>-70,88; -21,91</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,55</t>
+          <t>-3,31; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,18</t>
+          <t>-2,16; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,58</t>
+          <t>-5,8; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,63</t>
+          <t>-3,34; 3,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,95</t>
+          <t>-3,58; 0,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,52</t>
+          <t>-1,73; 2,83</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,55; 80,56</t>
+          <t>-67,04; 92,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 156,87</t>
+          <t>-47,35; 168,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 19,94</t>
+          <t>-45,95; 19,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 46,89</t>
+          <t>-26,09; 48,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 16,61</t>
+          <t>-45,08; 16,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 44,04</t>
+          <t>-21,03; 50,47</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,85</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,28</t>
+          <t>-4,31; -0,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,89</t>
+          <t>-0,49; 5,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 2,66</t>
+          <t>-4,7; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,84</t>
+          <t>-3,16; 3,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,65</t>
+          <t>-3,71; 0,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,81</t>
+          <t>-0,92; 3,49</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,32; 30,57</t>
+          <t>-92,6; 24,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 315,42</t>
+          <t>-13,59; 374,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 67,76</t>
+          <t>-57,94; 63,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 64,24</t>
+          <t>-37,09; 83,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 19,15</t>
+          <t>-63,5; 21,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 105,5</t>
+          <t>-15,5; 101,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,1</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,38</t>
+          <t>-0,57; 2,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,81</t>
+          <t>1,87; 7,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,77; -0,67</t>
+          <t>-7,99; -0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 2,52</t>
+          <t>-3,92; 3,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,35</t>
+          <t>-3,51; 0,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,13</t>
+          <t>-0,16; 4,19</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>811,19%</t>
+          <t>720,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-17,9%</t>
+          <t>-0,36%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>103,14; —</t>
+          <t>25,46; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,71; -8,4</t>
+          <t>-71,91; -7,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,15; 35,53</t>
+          <t>-33,97; 58,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,55; 15,09</t>
+          <t>-61,46; 9,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 111,11</t>
+          <t>-4,6; 115,69</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-12,54</t>
+          <t>-11,87</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,21</t>
+          <t>-7,07</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,53</t>
+          <t>-2,27; 5,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 0,27</t>
+          <t>-5,33; 0,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -1,87</t>
+          <t>-13,84; -1,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -7,76</t>
+          <t>-17,67; -7,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,41</t>
+          <t>-7,21; 0,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -4,32</t>
+          <t>-10,52; -4,15</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-62,06%</t>
+          <t>-65,75%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-77,57%</t>
+          <t>-73,39%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-72,97%</t>
+          <t>-71,51%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 317,29</t>
+          <t>-44,42; 338,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,27; 61,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-72,37; -12,44</t>
+          <t>-71,04; -11,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-89,38; -60,94</t>
+          <t>-84,52; -56,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 5,87</t>
+          <t>-58,67; 1,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,94; -54,99</t>
+          <t>-82,63; -52,43</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,97; -0,32</t>
+          <t>-5,02; -0,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,54</t>
+          <t>-1,4; 4,97</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,56</t>
+          <t>-3,77; 6,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,34</t>
+          <t>-6,16; 2,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,14</t>
+          <t>-3,17; 2,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,07</t>
+          <t>-2,48; 2,81</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-17,57%</t>
+          <t>-17,44%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,47</t>
+          <t>-94,03; 43,92</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 291,44</t>
+          <t>-31,53; 257,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 115,15</t>
+          <t>-33,99; 94,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 40,09</t>
+          <t>-53,59; 33,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 43,73</t>
+          <t>-45,23; 52,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 74,13</t>
+          <t>-33,63; 64,87</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>3,62</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; -0,07</t>
+          <t>-2,95; 0,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,64</t>
+          <t>0,35; 4,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,78</t>
+          <t>-3,9; 0,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,65</t>
+          <t>2,04; 7,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,1</t>
+          <t>-2,9; -0,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,53</t>
+          <t>1,74; 5,3</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-86,82; 12,82</t>
+          <t>-85,18; 15,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 281,58</t>
+          <t>7,84; 292,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,55; 19,74</t>
+          <t>-54,52; 20,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 112,7</t>
+          <t>27,59; 171,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,4; -1,85</t>
+          <t>-57,98; 0,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 127,81</t>
+          <t>32,25; 150,74</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,8</t>
+          <t>-1,21; 1,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,58</t>
+          <t>-0,56; 2,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,62</t>
+          <t>-1,85; 3,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,03</t>
+          <t>-1,66; 3,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,73</t>
+          <t>-1,16; 1,86</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,65</t>
+          <t>-0,57; 2,22</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 162,2</t>
+          <t>-44,96; 153,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 123,76</t>
+          <t>-29,27; 209,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 50,21</t>
+          <t>-26,78; 65,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 61,41</t>
+          <t>-22,14; 61,1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 51,1</t>
+          <t>-24,09; 55,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 46,75</t>
+          <t>-11,84; 64,28</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,29</t>
+          <t>-1,39; 0,18</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,1</t>
+          <t>0,46; 2,19</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,08</t>
+          <t>-2,63; -0,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,39</t>
+          <t>-1,31; 1,23</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,25</t>
+          <t>-1,6; -0,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,07</t>
+          <t>-0,12; 1,39</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-0,31%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 13,85</t>
+          <t>-45,85; 9,1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4,66; 95,98</t>
+          <t>16,14; 106,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-30,63; -1,05</t>
+          <t>-30,25; -0,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 5,49</t>
+          <t>-15,2; 16,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-30,04; -4,63</t>
+          <t>-28,7; -4,15</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 21,51</t>
+          <t>-2,14; 28,15</t>
         </is>
       </c>
     </row>
